--- a/genset1_readings.xlsx
+++ b/genset1_readings.xlsx
@@ -6,7 +6,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="135" windowWidth="20055" windowHeight="7695" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="genset_readings" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="genset1_readings" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
